--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0002T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0002T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.80412322242111</v>
+        <v>5.49317002364343</v>
       </c>
       <c r="D2" t="n">
-        <v>33.74038712218572</v>
+        <v>5.482812907355179</v>
       </c>
       <c r="E2" t="n">
-        <v>12.23387099271517</v>
+        <v>1.988004036316215</v>
       </c>
       <c r="F2" t="n">
-        <v>4.999547138448309</v>
+        <v>0.8124264099978505</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.571676580574089</v>
+        <v>0.7428974443432895</v>
       </c>
       <c r="D3" t="n">
-        <v>21.52324325003088</v>
+        <v>3.497527028130019</v>
       </c>
       <c r="E3" t="n">
-        <v>12.23387099271517</v>
+        <v>1.988004036316215</v>
       </c>
       <c r="F3" t="n">
-        <v>4.999547138448309</v>
+        <v>0.8124264099978505</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.47806232959902</v>
+        <v>2.190185128559841</v>
       </c>
       <c r="D4" t="n">
-        <v>28.36370920736567</v>
+        <v>4.609102746196921</v>
       </c>
       <c r="E4" t="n">
-        <v>12.23387099271517</v>
+        <v>1.988004036316215</v>
       </c>
       <c r="F4" t="n">
-        <v>4.999547138448309</v>
+        <v>0.8124264099978505</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
